--- a/output/2026-10-03_22_Malesia_Pulau_Pinang_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-03_22_Malesia_Pulau_Pinang_Impiantistica_aspirazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Engineering/manufacturer/installer di Air Pollution Control Systems (wet scrubber, dust collector, welding fume collector, thermal oxidizer, fume hood). Confermato via sito ufficiale e investpenang.gov.my SME directory.</t>
+          <t>Engineering/manufacturer/installer di Air Pollution Control Systems (wet scrubber, dust collector, welding fume collector, thermal oxidizer, fume hood). Confermato via sito ufficiale e investpenang.gov.my SME directory. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
